--- a/Data/Home/Balcony.AirQuality.xlsx
+++ b/Data/Home/Balcony.AirQuality.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1710743736</v>
+        <v>1714132517</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,134 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1711050082</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Balcony.AirQuality.state: Good</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1711066330</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Balcony.AirQuality.state: Excellent</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1711451807</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Balcony.AirQuality.state: Good</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AirQuality_Change</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Balcony</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1711462366</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Balcony.AirQuality.state: Excellent</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
